--- a/Microcontrolador.xlsx
+++ b/Microcontrolador.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://estudianteccr-my.sharepoint.com/personal/joprendas_estudiantec_cr/Documents/TEC/IX Semestre/Micros/Proyecto final/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jdpre\OneDrive\Documentos\Micros\PROYECTO-FINAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="8_{675D30B1-01FE-4093-9D0D-795ACD98533D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96934DB9-A116-4022-9C2B-1D912D082E6A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8A9E37-7D31-4582-A538-BD7D55C5B156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2CE97A2C-A60B-4463-AD41-D658393164D3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>STM32 nucleo</t>
   </si>
@@ -125,6 +125,63 @@
   </si>
   <si>
     <t>Buscar las hojas de dato en "Richard electronics"</t>
+  </si>
+  <si>
+    <t>Componentes</t>
+  </si>
+  <si>
+    <t>Precio</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0d6ipAPT Ó https://a.co/d/01CrGF4w Ó https://a.co/d/00pmVhze</t>
+  </si>
+  <si>
+    <t>https://a.co/d/06HmM8iU</t>
+  </si>
+  <si>
+    <t>https://a.co/d/08gJBjwB</t>
+  </si>
+  <si>
+    <t>Paquete de jumpers</t>
+  </si>
+  <si>
+    <t>Paquete de 4 servomotores</t>
+  </si>
+  <si>
+    <t>Micros</t>
+  </si>
+  <si>
+    <t>Sensores</t>
+  </si>
+  <si>
+    <t>Paquete de dos sensores ultrasonicos</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0ihfly8O</t>
+  </si>
+  <si>
+    <t>Paquete de 3 sensores infrarrojos (cortos)</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0gYHSE7h</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0iKCGpte</t>
+  </si>
+  <si>
+    <t>Sensor infrarrojo (largo)</t>
+  </si>
+  <si>
+    <t>https://a.co/d/09Ya2usR</t>
+  </si>
+  <si>
+    <t>Sensor laser</t>
   </si>
 </sst>
 </file>
@@ -134,7 +191,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,8 +220,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,8 +271,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -207,11 +313,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -235,6 +394,59 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -302,13 +514,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1862415</xdr:colOff>
+      <xdr:colOff>1895072</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>852</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>322803</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>725574</xdr:colOff>
       <xdr:row>54</xdr:row>
       <xdr:rowOff>114209</xdr:rowOff>
     </xdr:to>
@@ -333,8 +545,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11716460" y="6633716"/>
-          <a:ext cx="5941843" cy="6780857"/>
+          <a:off x="11746643" y="6619366"/>
+          <a:ext cx="5927988" cy="6590357"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -715,6 +927,10 @@
     <col min="4" max="4" width="27.77734375" customWidth="1"/>
     <col min="5" max="5" width="39.33203125" customWidth="1"/>
     <col min="6" max="6" width="27.77734375" customWidth="1"/>
+    <col min="8" max="8" width="64.109375" customWidth="1"/>
+    <col min="9" max="9" width="32.6640625" customWidth="1"/>
+    <col min="10" max="10" width="120.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
@@ -767,7 +983,7 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="38.4" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A3" s="1"/>
       <c r="B3" s="3" t="s">
         <v>2</v>
@@ -785,7 +1001,9 @@
         <v>25</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="H3" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -815,9 +1033,7 @@
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="8" t="s">
-        <v>28</v>
-      </c>
+      <c r="H4" s="8"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -847,9 +1063,15 @@
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+      <c r="H5" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -879,13 +1101,20 @@
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+      <c r="H6" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="24">
+        <v>6990</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>33</v>
+      </c>
       <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="L6" s="21" t="s">
+        <v>38</v>
+      </c>
       <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -913,11 +1142,19 @@
         <v>10000</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
+      <c r="H7" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="24">
+        <v>7945</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>34</v>
+      </c>
       <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="L7" s="22" t="s">
+        <v>39</v>
+      </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -939,9 +1176,15 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
+      <c r="H8" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="24">
+        <v>4672</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>35</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -967,9 +1210,15 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
+      <c r="H9" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="27">
+        <v>3270</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>41</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -997,9 +1246,15 @@
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
+      <c r="H10" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="27">
+        <v>3270</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>43</v>
+      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1029,9 +1284,15 @@
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
+      <c r="H11" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="27">
+        <v>6080</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>44</v>
+      </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1061,9 +1322,15 @@
         <v>21</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
+      <c r="H12" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="I12" s="27">
+        <v>6075</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>46</v>
+      </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -1085,9 +1352,11 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="18">
+        <v>0</v>
+      </c>
+      <c r="J13" s="16"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1101,7 +1370,7 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="1"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -1109,9 +1378,11 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="18">
+        <v>0</v>
+      </c>
+      <c r="J14" s="17"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1125,7 +1396,7 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="1"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1133,9 +1404,14 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
+      <c r="H15" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="20">
+        <f>SUM(I6:I14)</f>
+        <v>38302</v>
+      </c>
+      <c r="J15" s="10"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -1157,8 +1433,8 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
